--- a/data/file_generation/input/data_57/丹麦超开赛时间_2025-10-27_01_00哥本哈根_VS维堡_比分0-0(0-0)标盘明细.xlsx
+++ b/data/file_generation/input/data_57/丹麦超开赛时间_2025-10-27_01_00哥本哈根_VS维堡_比分0-0(0-0)标盘明细.xlsx
@@ -27722,26 +27722,18 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
+  <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B163B78-EE43-4CE6-9A30-1B0599415229}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7C39FF8-3B11-4BD6-8FC8-76CB2EF79F3E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAB117A5-888A-493E-B1D2-6E87A5C0C2C7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C84F1308-CE35-43D6-A3C0-7AC77DC6C28E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAFC910B-EBAA-4571-924C-6695E4B4863D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47340616-A21A-4A9E-9796-A534F9F4615A}"/>
 </file>